--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,6 +468,36 @@
         <is>
           <t>입고수량</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1785192393964</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>가스켓</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,9 +495,47 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
       <c r="H2" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1785192869534</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="n">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,6 +536,42 @@
       </c>
       <c r="H3" t="n">
         <v>120</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1785192921322</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,6 +572,36 @@
       </c>
       <c r="H4" t="n">
         <v>36</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1785192936758</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>가스켓</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,9 +599,47 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
       <c r="H5" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1785194784595</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>70</v>
+      </c>
+      <c r="H6" t="n">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -640,6 +640,36 @@
       </c>
       <c r="H6" t="n">
         <v>120</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1785194793460</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>가스켓</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,9 +667,47 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
       <c r="H7" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1785195009007</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PALL</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>70</v>
+      </c>
+      <c r="H8" t="n">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -710,6 +710,42 @@
         <v>120</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1785199837567</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>HP-F8701</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,6 +746,36 @@
         <v>24</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1785200238604</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>가스켓</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HP-F8701</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,36 +746,6 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1785200238604</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>가스켓</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>7블럭</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>HP-F8701</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,6 +746,42 @@
         <v>24</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1785200611758</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PALL</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>70</v>
+      </c>
+      <c r="H10" t="n">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,6 +782,42 @@
         <v>36</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1785200938438</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AR-F5106</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,42 +782,6 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1785200938438</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>필터</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AR-F5106</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>15</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,6 +782,42 @@
         <v>36</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1785201050256</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AR-F5106 (12"x300#)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,7 +712,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1785199837567</v>
+        <v>1785200611758</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -726,29 +726,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7블럭</t>
+          <t>10블럭</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HP-F8701</t>
+          <t>AR-F5103A</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>신우</t>
+          <t>PALL</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H9" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1785200611758</v>
+        <v>1785201050256</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -767,54 +767,18 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AR-F5103A</t>
+          <t>AR-F5106 (12"x300#)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PALL</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1785201050256</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>필터</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AR-F5106 (12"x300#)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
         <v>15</v>
       </c>
     </row>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,6 +782,42 @@
         <v>15</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1785201216437</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HP-F8701 (12"x300#)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,6 +818,42 @@
         <v>24</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1785201309703</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PALL</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>40</v>
+      </c>
+      <c r="H12" t="n">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -854,6 +854,36 @@
         <v>18</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1785207522463</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>가스켓</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>TG-F7103</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -879,9 +879,47 @@
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
       <c r="H13" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1785207533258</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TG-F7103</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>50</v>
+      </c>
+      <c r="H14" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,6 +922,42 @@
         <v>30</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1785207557748</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>50</v>
+      </c>
+      <c r="H15" t="n">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,6 +958,36 @@
         <v>120</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1785207563991</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>가스켓</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,9 +983,41 @@
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
       <c r="H16" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1786081344070</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>가스켓</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,9 +1015,47 @@
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
       <c r="H17" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1787200237406</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>100</v>
+      </c>
+      <c r="H18" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1058,6 +1058,42 @@
         <v>36</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1788139560475</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>HP-F8701 (12"x300#)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>240</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1094,6 +1094,42 @@
         <v>240</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1788139571025</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>50</v>
+      </c>
+      <c r="H20" t="n">
+        <v>360</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
